--- a/artfynd/A 47921-2024 artfynd.xlsx
+++ b/artfynd/A 47921-2024 artfynd.xlsx
@@ -3333,7 +3333,7 @@
         <v>121376820</v>
       </c>
       <c r="B26" t="n">
-        <v>91249</v>
+        <v>91259</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>

--- a/artfynd/A 47921-2024 artfynd.xlsx
+++ b/artfynd/A 47921-2024 artfynd.xlsx
@@ -3333,7 +3333,7 @@
         <v>121376820</v>
       </c>
       <c r="B26" t="n">
-        <v>91259</v>
+        <v>91271</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>

--- a/artfynd/A 47921-2024 artfynd.xlsx
+++ b/artfynd/A 47921-2024 artfynd.xlsx
@@ -3333,7 +3333,7 @@
         <v>121376820</v>
       </c>
       <c r="B26" t="n">
-        <v>91271</v>
+        <v>91272</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>

--- a/artfynd/A 47921-2024 artfynd.xlsx
+++ b/artfynd/A 47921-2024 artfynd.xlsx
@@ -3333,7 +3333,7 @@
         <v>121376820</v>
       </c>
       <c r="B26" t="n">
-        <v>91272</v>
+        <v>91275</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>

--- a/artfynd/A 47921-2024 artfynd.xlsx
+++ b/artfynd/A 47921-2024 artfynd.xlsx
@@ -3333,7 +3333,7 @@
         <v>121376820</v>
       </c>
       <c r="B26" t="n">
-        <v>91275</v>
+        <v>91281</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>

--- a/artfynd/A 47921-2024 artfynd.xlsx
+++ b/artfynd/A 47921-2024 artfynd.xlsx
@@ -3333,7 +3333,7 @@
         <v>121376820</v>
       </c>
       <c r="B26" t="n">
-        <v>91281</v>
+        <v>91282</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>

--- a/artfynd/A 47921-2024 artfynd.xlsx
+++ b/artfynd/A 47921-2024 artfynd.xlsx
@@ -3333,7 +3333,7 @@
         <v>121376820</v>
       </c>
       <c r="B26" t="n">
-        <v>91282</v>
+        <v>91290</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>

--- a/artfynd/A 47921-2024 artfynd.xlsx
+++ b/artfynd/A 47921-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2676,37 +2676,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>103565558</v>
+        <v>98473643</v>
       </c>
       <c r="B20" t="n">
-        <v>56411</v>
+        <v>96251</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>219790</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2716,13 +2716,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>817450.5769632335</v>
+        <v>817556.6779855045</v>
       </c>
       <c r="R20" t="n">
-        <v>7373679.531172755</v>
+        <v>7373428.603837174</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2022-08-11</t>
+          <t>2021-06-22</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2022-08-11</t>
+          <t>2021-06-22</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -2776,22 +2776,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Elias Forsberg</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Elias Forsberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>98473643</v>
+        <v>98473705</v>
       </c>
       <c r="B21" t="n">
-        <v>96251</v>
+        <v>96354</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2804,21 +2804,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2828,10 +2828,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>817556.6779855045</v>
+        <v>817543.8455759927</v>
       </c>
       <c r="R21" t="n">
-        <v>7373428.603837174</v>
+        <v>7373416.602929476</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2900,50 +2900,50 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>98473705</v>
+        <v>120460358</v>
       </c>
       <c r="B22" t="n">
-        <v>96354</v>
+        <v>82374</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221952</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Granlandshögstet, Nb</t>
+          <t>Nedre Granlandet, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>817543.8455759927</v>
+        <v>817467</v>
       </c>
       <c r="R22" t="n">
-        <v>7373416.602929476</v>
+        <v>7373685</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2970,22 +2970,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2021-06-22</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2021-06-22</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3000,22 +2990,26 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Elias Forsberg</t>
+          <t>Torbjörn Josefsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Elias Forsberg</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120460358</v>
+        <v>120460331</v>
       </c>
       <c r="B23" t="n">
-        <v>82374</v>
+        <v>78590</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3028,21 +3022,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3052,10 +3046,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>817467</v>
+        <v>817417</v>
       </c>
       <c r="R23" t="n">
-        <v>7373685</v>
+        <v>7373700</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3118,7 +3112,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120460331</v>
+        <v>120460332</v>
       </c>
       <c r="B24" t="n">
         <v>78590</v>
@@ -3158,10 +3152,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>817417</v>
+        <v>817457</v>
       </c>
       <c r="R24" t="n">
-        <v>7373700</v>
+        <v>7373632</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3224,10 +3218,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120460332</v>
+        <v>121376820</v>
       </c>
       <c r="B25" t="n">
-        <v>78590</v>
+        <v>91290</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3236,25 +3230,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3264,13 +3258,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>817457</v>
+        <v>817432</v>
       </c>
       <c r="R25" t="n">
-        <v>7373632</v>
+        <v>7373763</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3323,112 +3317,6 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr">
-        <is>
-          <t>Ecogain</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>121376820</v>
-      </c>
-      <c r="B26" t="n">
-        <v>91290</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>760</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Doftticka</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Haploporus odorus</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Nedre Granlandet, Nb</t>
-        </is>
-      </c>
-      <c r="Q26" t="n">
-        <v>817432</v>
-      </c>
-      <c r="R26" t="n">
-        <v>7373763</v>
-      </c>
-      <c r="S26" t="n">
-        <v>25</v>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>Boden</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>Råneå</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>2024-06-20</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>2024-06-20</t>
-        </is>
-      </c>
-      <c r="AD26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="inlineStr"/>
-      <c r="AW26" t="inlineStr">
-        <is>
-          <t>Torbjörn Josefsson</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>Torbjörn Josefsson</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
         <is>
           <t>Ecogain artbingo</t>
         </is>
